--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R35799cb41a2e4d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R18cd30ab76164dba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,28 +334,28 @@
         <x:v>辅助工具</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>PowerShell或系统终端、CSV与NDJSON查看器</x:v>
+        <x:v>系统终端、CSV与NDJSON查看器</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="33" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>输入来源</x:v>
+        <x:v>业务输入来源</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>脱敏聊天室分片、成员清单、投递回执和敏感内容规则</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="33" customHeight="1">
+        <x:v>本批客服聊天室消息分片、成员清单、投递回执和敏感内容规则，人员与房间字段已经脱敏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>解压输入数据包后在input_data目录读取本地材料</x:v>
+        <x:v>恢复各房间的可见消息顺序，记录敏感内容处置和投递缺口，为客服质检、风控、消息平台与运营提供可追溯材料</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>输入材料</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
         <x:v>shard_messages/*.jsonl；room_members.csv；receipt_log.csv；moderation_rules.json；starter/rebuild_chat_transcripts.mjs</x:v>
@@ -363,18 +363,18 @@
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
         <x:v>output/scripts/rebuild_chat_transcripts.mjs；output/reports/room_transcripts.ndjson；output/reports/moderation_actions.csv；output/reports/receipt_gaps.csv；output/reports/room_summary.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件操作步骤</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>归并事件；选择版本；整理顺序；遮盖文本；关联回执；定位缺口；汇总房间</x:v>
+        <x:v>读取消息分片，折叠重复事件，选择最终版本，整理房间顺序，依次遮盖文本，关联投递回执，定位缺口并归集房间汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" customHeight="1">
@@ -422,23 +422,23 @@
         <x:v>房间汇总</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>由消息版本、转写、遮盖动作和回执缺口归集，不按房间名称预设结果</x:v>
+        <x:v>由消息版本、转写、遮盖动作和回执缺口归集</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>离线边界</x:v>
+        <x:v>处理边界</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>正式处理不访问真实聊天服务、远程存储或外部接口</x:v>
+        <x:v>消息分片、成员清单、投递回执和规则文件作为只读业务材料，交付只写入output目录</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>报告交接</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>Node.js入口正常结束，完成程序与四份业务报告可读且能按业务主键互相追溯</x:v>
+        <x:v>房间转写交给客服质检，遮盖动作交给风控，投递缺口交给消息平台，房间汇总交给运营</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="33" customHeight="1">
@@ -451,10 +451,10 @@
     </x:row>
     <x:row r="19" ht="33" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>实现自由度</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>函数拆分、内部容器、文件访问次序、对象键序、CSV引号和本机路径可以不同</x:v>
+        <x:v>函数拆分、内部容器、文件访问次序、对象键序和CSV序列化方式可以不同，业务关系与交付字段保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
